--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowDetailTemplate.xlsx
@@ -740,11 +740,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1275,26 +1278,26 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="17.8166666666667" customWidth="1"/>
-    <col min="2" max="3" width="15.5416666666667" customWidth="1"/>
-    <col min="4" max="4" width="17.8166666666667" customWidth="1"/>
-    <col min="5" max="5" width="19.725" customWidth="1"/>
+    <col min="1" max="1" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="2" max="3" width="15.5416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.725" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowDetailTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowDetailTemplate.xlsx
@@ -27,29 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>借出人</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
       <rPr>
@@ -1275,16 +1253,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.8166666666667" style="1" customWidth="1"/>
-    <col min="2" max="3" width="15.5416666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.8166666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.725" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.5416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.725" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1294,11 +1271,8 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
